--- a/tests/fixtures/cost_calc/ПРИМЕР_обсчета_24_06.xlsx
+++ b/tests/fixtures/cost_calc/ПРИМЕР_обсчета_24_06.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,11 @@
       <c r="C3" t="n">
         <v>1.15</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>гр.2 = код нормы ГЭСН из сборника</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -767,6 +772,11 @@
       <c r="E4" t="n">
         <v>3941192.27</v>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>гр.7 = гр.5 * гр.6 (норма × коэффициент)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -787,6 +797,15 @@
       <c r="E6" t="n">
         <v>127906.66</v>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>выбор расценки производится из гр.8 сплит-формы</t>
+        </is>
+      </c>
+      <c r="Z6">
+        <f>R6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -807,6 +826,15 @@
       <c r="E8" t="n">
         <v>4333793.6</v>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Код ресурса на машинистов определяется из состава машин (4-100-NN по разряду)</t>
+        </is>
+      </c>
+      <c r="Z8">
+        <f>Z6</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -830,6 +858,11 @@
       <c r="E10" t="n">
         <v>3683191.41</v>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>если в гр.8 сплит-формы прочерк — берётся КАЦ/ТЦ (текущая цена)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +886,11 @@
       <c r="E12" t="n">
         <v>10472445.95</v>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>коэффициент 1.15 применяется к ОЗП/ЭМ/ЗПМ (Приказ 55/пр), материалы — без коэффициента</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -874,6 +912,10 @@
       <c r="E13" t="n">
         <v>6354837.24</v>
       </c>
+      <c r="Z13">
+        <f>Z12</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,6 +925,10 @@
       </c>
       <c r="E14" t="n">
         <v>16827283.19</v>
+      </c>
+      <c r="Z14">
+        <f>Z13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
